--- a/imageCreationExcel/Bright/Master/MASTER_4.xlsx
+++ b/imageCreationExcel/Bright/Master/MASTER_4.xlsx
@@ -552,15 +552,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_busy\7_day_sun_busy.jpg</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>25.454</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>1.064</v>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>M_4_1_E_filler_7_day_sun_busy_MODEL.jpg</t>
+          <t>M_4_1_E_filler_7_day_sun_busy_MODEL_brightness25.454_contrast1.160_gamma1.064.jpg</t>
         </is>
       </c>
     </row>
@@ -606,15 +624,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_busy\1_day_rain_busy.jpg</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>36.09</v>
+      </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>M_4_2_1_match_1_day_rain_busy_BRIGHTONLY.jpg</t>
+          <t>M_4_2_1_match_1_day_rain_busy_BRIGHTONLY_brightness36.090.jpg</t>
         </is>
       </c>
     </row>
@@ -660,15 +684,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_busy\3_day_sun_busy.jpg</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>45.47</v>
+      </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>M_4_3_T_filler_3_day_sun_busy_BRIGHTONLY.jpg</t>
+          <t>M_4_3_T_filler_3_day_sun_busy_BRIGHTONLY_brightness45.470.jpg</t>
         </is>
       </c>
     </row>
@@ -822,15 +852,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_busy\6_day_rain_busy.jpg</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>36.09</v>
+      </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>M_4_6_8_unmatch_6_day_rain_busy_BRIGHTONLY.jpg</t>
+          <t>M_4_6_8_unmatch_6_day_rain_busy_BRIGHTONLY_brightness36.090.jpg</t>
         </is>
       </c>
     </row>
@@ -984,15 +1020,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_busy\2_day_rain_busy.jpg</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>23.168</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>1.169</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>1.078</v>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>M_4_9_R_filler_2_day_rain_busy_MODEL.jpg</t>
+          <t>M_4_9_R_filler_2_day_rain_busy_MODEL_brightness23.168_contrast1.169_gamma1.078.jpg</t>
         </is>
       </c>
     </row>
@@ -1038,15 +1092,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_empty\7_day_sun_empty.jpg</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>18.052</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>1.163</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>1.019</v>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>M_4_10_L_filler_7_day_sun_empty_MODEL.jpg</t>
+          <t>M_4_10_L_filler_7_day_sun_empty_MODEL_brightness18.052_contrast1.163_gamma1.019.jpg</t>
         </is>
       </c>
     </row>
@@ -1146,15 +1218,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_empty\5_day_rain_empty.jpg</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>22.602</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>1.158</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>1.045</v>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>M_4_12_5_match_5_day_rain_empty_MODEL.jpg</t>
+          <t>M_4_12_5_match_5_day_rain_empty_MODEL_brightness22.602_contrast1.158_gamma1.045.jpg</t>
         </is>
       </c>
     </row>
@@ -1308,15 +1398,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_empty\3_day_sun_empty.jpg</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>40.55</v>
+      </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>M_4_15_R_filler_3_day_sun_empty_BRIGHTONLY.jpg</t>
+          <t>M_4_15_R_filler_3_day_sun_empty_BRIGHTONLY_brightness40.550.jpg</t>
         </is>
       </c>
     </row>
@@ -1362,15 +1458,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_busy\5_day_rain_busy.jpg</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>36.09</v>
+      </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>M_4_16_D_filler_5_day_rain_busy_BRIGHTONLY.jpg</t>
+          <t>M_4_16_D_filler_5_day_rain_busy_BRIGHTONLY_brightness36.090.jpg</t>
         </is>
       </c>
     </row>
@@ -1416,15 +1518,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_empty\4_day_rain_empty.jpg</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>22.602</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>1.158</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>1.045</v>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>M_4_17_7_unmatch_4_day_rain_empty_MODEL.jpg</t>
+          <t>M_4_17_7_unmatch_4_day_rain_empty_MODEL_brightness22.602_contrast1.158_gamma1.045.jpg</t>
         </is>
       </c>
     </row>
@@ -1524,15 +1644,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_empty\8_day_sun_empty.jpg</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>40.55</v>
+      </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>M_4_19_5_unmatch_8_day_sun_empty_BRIGHTONLY.jpg</t>
+          <t>M_4_19_5_unmatch_8_day_sun_empty_BRIGHTONLY_brightness40.550.jpg</t>
         </is>
       </c>
     </row>
@@ -1578,15 +1704,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_busy\4_day_rain_busy.jpg</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>36.09</v>
+      </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>M_4_20_J_filler_4_day_rain_busy_BRIGHTONLY.jpg</t>
+          <t>M_4_20_J_filler_4_day_rain_busy_BRIGHTONLY_brightness36.090.jpg</t>
         </is>
       </c>
     </row>
@@ -1632,15 +1764,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_empty\7_day_rain_empty.jpg</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>22.602</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
+        <v>1.158</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>1.045</v>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>M_4_21_R_filler_7_day_rain_empty_MODEL.jpg</t>
+          <t>M_4_21_R_filler_7_day_rain_empty_MODEL_brightness22.602_contrast1.158_gamma1.045.jpg</t>
         </is>
       </c>
     </row>
@@ -1686,15 +1836,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_busy\8_day_sun_busy.jpg</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>45.47</v>
+      </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>M_4_22_4_unmatch_8_day_sun_busy_BRIGHTONLY.jpg</t>
+          <t>M_4_22_4_unmatch_8_day_sun_busy_BRIGHTONLY_brightness45.470.jpg</t>
         </is>
       </c>
     </row>
@@ -1794,15 +1950,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_busy\5_day_sun_busy.jpg</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>45.47</v>
+      </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>M_4_24_L_filler_5_day_sun_busy_BRIGHTONLY.jpg</t>
+          <t>M_4_24_L_filler_5_day_sun_busy_BRIGHTONLY_brightness45.470.jpg</t>
         </is>
       </c>
     </row>
@@ -1848,15 +2010,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_busy\8_day_rain_busy.jpg</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>36.09</v>
+      </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>M_4_25_R_filler_8_day_rain_busy_BRIGHTONLY.jpg</t>
+          <t>M_4_25_R_filler_8_day_rain_busy_BRIGHTONLY_brightness36.090.jpg</t>
         </is>
       </c>
     </row>
@@ -1902,15 +2070,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_empty\3_day_rain_empty.jpg</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>22.602</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M27" t="n">
+        <v>1.158</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O27" t="n">
+        <v>1.045</v>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>M_4_26_5_unmatch_3_day_rain_empty_MODEL.jpg</t>
+          <t>M_4_26_5_unmatch_3_day_rain_empty_MODEL_brightness22.602_contrast1.158_gamma1.045.jpg</t>
         </is>
       </c>
     </row>
@@ -1956,15 +2142,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_busy\4_day_rain_busy.jpg</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>23.168</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M28" t="n">
+        <v>1.169</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O28" t="n">
+        <v>1.078</v>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>M_4_27_R_filler_4_day_rain_busy_MODEL.jpg</t>
+          <t>M_4_27_R_filler_4_day_rain_busy_MODEL_brightness23.168_contrast1.169_gamma1.078.jpg</t>
         </is>
       </c>
     </row>
@@ -2064,15 +2268,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_empty\2_day_sun_empty.jpg</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>40.55</v>
+      </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>M_4_29_A_filler_2_day_sun_empty_BRIGHTONLY.jpg</t>
+          <t>M_4_29_A_filler_2_day_sun_empty_BRIGHTONLY_brightness40.550.jpg</t>
         </is>
       </c>
     </row>
@@ -2118,15 +2328,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_empty\8_day_rain_empty.jpg</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>22.602</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M31" t="n">
+        <v>1.158</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O31" t="n">
+        <v>1.045</v>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>M_4_30_U_filler_8_day_rain_empty_MODEL.jpg</t>
+          <t>M_4_30_U_filler_8_day_rain_empty_MODEL_brightness22.602_contrast1.158_gamma1.045.jpg</t>
         </is>
       </c>
     </row>
@@ -2280,15 +2508,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_empty\7_day_sun_empty.jpg</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>40.55</v>
+      </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>M_4_33_R_filler_7_day_sun_empty_BRIGHTONLY.jpg</t>
+          <t>M_4_33_R_filler_7_day_sun_empty_BRIGHTONLY_brightness40.550.jpg</t>
         </is>
       </c>
     </row>
@@ -2334,15 +2568,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_empty\7_day_sun_empty.jpg</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>18.052</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M35" t="n">
+        <v>1.163</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O35" t="n">
+        <v>1.019</v>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>M_4_34_7_match_7_day_sun_empty_MODEL.jpg</t>
+          <t>M_4_34_7_match_7_day_sun_empty_MODEL_brightness18.052_contrast1.163_gamma1.019.jpg</t>
         </is>
       </c>
     </row>
@@ -2388,15 +2640,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_busy\0_day_sun_busy.jpg</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>25.454</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M36" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O36" t="n">
+        <v>1.064</v>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>M_4_35_F_filler_0_day_sun_busy_MODEL.jpg</t>
+          <t>M_4_35_F_filler_0_day_sun_busy_MODEL_brightness25.454_contrast1.160_gamma1.064.jpg</t>
         </is>
       </c>
     </row>
@@ -2496,15 +2766,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_busy\7_day_sun_busy.jpg</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>25.454</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M38" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O38" t="n">
+        <v>1.064</v>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>M_4_37_L_filler_7_day_sun_busy_MODEL.jpg</t>
+          <t>M_4_37_L_filler_7_day_sun_busy_MODEL_brightness25.454_contrast1.160_gamma1.064.jpg</t>
         </is>
       </c>
     </row>
@@ -2658,15 +2946,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_busy\2_day_rain_busy.jpg</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>36.09</v>
+      </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>M_4_40_9_unmatch_2_day_rain_busy_BRIGHTONLY.jpg</t>
+          <t>M_4_40_9_unmatch_2_day_rain_busy_BRIGHTONLY_brightness36.090.jpg</t>
         </is>
       </c>
     </row>
@@ -2712,15 +3006,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_busy\4_day_sun_busy.jpg</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>25.454</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M42" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O42" t="n">
+        <v>1.064</v>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>M_4_41_T_filler_4_day_sun_busy_MODEL.jpg</t>
+          <t>M_4_41_T_filler_4_day_sun_busy_MODEL_brightness25.454_contrast1.160_gamma1.064.jpg</t>
         </is>
       </c>
     </row>
@@ -2766,15 +3078,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_empty\4_day_rain_empty.jpg</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>35.62</v>
+      </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>M_4_42_F_filler_4_day_rain_empty_BRIGHTONLY.jpg</t>
+          <t>M_4_42_F_filler_4_day_rain_empty_BRIGHTONLY_brightness35.620.jpg</t>
         </is>
       </c>
     </row>
@@ -2874,15 +3192,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_busy\3_day_sun_busy.jpg</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
+        <v>25.454</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M45" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O45" t="n">
+        <v>1.064</v>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>M_4_44_I_filler_3_day_sun_busy_MODEL.jpg</t>
+          <t>M_4_44_I_filler_3_day_sun_busy_MODEL_brightness25.454_contrast1.160_gamma1.064.jpg</t>
         </is>
       </c>
     </row>
@@ -2928,15 +3264,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_busy\6_day_rain_busy.jpg</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
+        <v>23.168</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M46" t="n">
+        <v>1.169</v>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O46" t="n">
+        <v>1.078</v>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>M_4_45_6_match_6_day_rain_busy_MODEL.jpg</t>
+          <t>M_4_45_6_match_6_day_rain_busy_MODEL_brightness23.168_contrast1.169_gamma1.078.jpg</t>
         </is>
       </c>
     </row>
@@ -2982,15 +3336,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_empty\7_day_sun_empty.jpg</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
+        <v>40.55</v>
+      </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>M_4_46_L_filler_7_day_sun_empty_BRIGHTONLY.jpg</t>
+          <t>M_4_46_L_filler_7_day_sun_empty_BRIGHTONLY_brightness40.550.jpg</t>
         </is>
       </c>
     </row>
@@ -3036,15 +3396,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_busy\8_day_sun_busy.jpg</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
+        <v>25.454</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M48" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O48" t="n">
+        <v>1.064</v>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>M_4_47_8_match_8_day_sun_busy_MODEL.jpg</t>
+          <t>M_4_47_8_match_8_day_sun_busy_MODEL_brightness25.454_contrast1.160_gamma1.064.jpg</t>
         </is>
       </c>
     </row>
@@ -3090,15 +3468,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_empty\8_day_sun_empty.jpg</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
+        <v>40.55</v>
+      </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>M_4_48_T_filler_8_day_sun_empty_BRIGHTONLY.jpg</t>
+          <t>M_4_48_T_filler_8_day_sun_empty_BRIGHTONLY_brightness40.550.jpg</t>
         </is>
       </c>
     </row>
